--- a/05_school/データアクセス権限表.xlsx
+++ b/05_school/データアクセス権限表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yu-sugino\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yu-sugino\Downloads\workspace\14_extratask\05_school\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D83259E8-6724-4A0B-A497-6183EC0DFC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50657D5A-ECFC-4D61-A1CD-D67D6465A8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{DCAF8F53-2788-4BC2-9E7D-758CEC5A2C19}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{DCAF8F53-2788-4BC2-9E7D-758CEC5A2C19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -224,16 +224,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>閲覧(所属クラス)</t>
-    <rPh sb="0" eb="2">
-      <t>エツラン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ショゾク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>閲覧</t>
     <rPh sb="0" eb="2">
       <t>エツラン</t>
@@ -272,22 +262,35 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>編集(担当クラス)</t>
+    <t>閲覧(匿名化)</t>
     <rPh sb="0" eb="2">
-      <t>ヘンシュウ</t>
+      <t>エツラン</t>
     </rPh>
     <rPh sb="3" eb="5">
-      <t>タントウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>編集(自分のみ)</t>
+      <t>トクメイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>閲覧(対象校のみ)</t>
     <rPh sb="0" eb="2">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ジブン</t>
+      <t>エツラン</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>タイショウコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>閲覧(匿名化)</t>
+    <rPh sb="0" eb="2">
+      <t>エツラン</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>トクメイカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -991,13 +994,13 @@
         <v>21</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>47</v>
@@ -1014,13 +1017,13 @@
         <v>22</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>47</v>
@@ -1037,13 +1040,13 @@
         <v>23</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>47</v>
@@ -1060,13 +1063,13 @@
         <v>24</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>47</v>
@@ -1083,13 +1086,13 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>47</v>
@@ -1123,16 +1126,16 @@
         <v>49</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>50</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
@@ -1152,10 +1155,10 @@
         <v>47</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
@@ -1169,7 +1172,7 @@
         <v>50</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>50</v>
@@ -1192,7 +1195,7 @@
         <v>50</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>50</v>
@@ -1215,7 +1218,7 @@
         <v>28</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>10</v>
@@ -1243,13 +1246,13 @@
         <v>36</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>49</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>48</v>
@@ -1266,22 +1269,22 @@
         <v>37</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>48</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
@@ -1289,13 +1292,13 @@
         <v>38</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>48</v>
@@ -1318,7 +1321,7 @@
         <v>50</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>47</v>
@@ -1349,19 +1352,19 @@
         <v>46</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
